--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SanjaY\eclipse\eclipse\Workspace\AutomationFramework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB7F55F-B789-4A7D-8B73-1A0650FE29B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6002F0-BC6B-4480-A352-B458C9E81C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">Email </t>
   </si>
@@ -40,16 +40,37 @@
     <t>Maxpayne@3</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>sanjay</t>
+  </si>
+  <si>
+    <t>wrong123</t>
+  </si>
+  <si>
+    <t>Test@789</t>
+  </si>
+  <si>
+    <t>dummy@gmail.com</t>
+  </si>
+  <si>
     <t>wrong@gmail.com</t>
   </si>
   <si>
-    <t>wrong123</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>sanjay</t>
+    <t>rahul</t>
+  </si>
+  <si>
+    <t>amit</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>Invalid</t>
   </si>
 </sst>
 </file>
@@ -378,42 +399,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{05ADA764-9A4F-43D2-A798-7286ADA97EA1}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{70D8315A-88AF-40B1-BE53-D721C7C161B5}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{53B09C15-9685-4611-BE05-8CD62BFEBCEF}"/>
+    <hyperlink ref="B3" r:id="rId3" display="Maxpayne@3" xr:uid="{B6D1BEDA-6075-49B0-B351-1480CFF1AAF0}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{C7FACC52-6018-40FD-8A3F-E1D7DD6CD4D5}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{5DC358F5-5B75-4F15-AA75-E5B1E40DAA75}"/>
+    <hyperlink ref="A4" r:id="rId6" xr:uid="{FFF79F23-E68C-4C98-B6C6-B37126B9E7ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -421,17 +465,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD4AE4F6-57D6-4F68-ABD4-BBE04D371EA3}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
